--- a/data/rules/sourceConfig.xlsx
+++ b/data/rules/sourceConfig.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC95F64-72DC-3745-9B0D-2F9E17B60B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5202C96-8C65-2C4D-9915-E37D50EAAB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15920" xr2:uid="{CD5289B5-C06B-194A-96AE-6288D441C4BC}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>source</t>
   </si>
@@ -43,9 +43,6 @@
     <t>entity_field</t>
   </si>
   <si>
-    <t>DAFT</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -56,6 +53,18 @@
   </si>
   <si>
     <t>OFAC-NON-SDN</t>
+  </si>
+  <si>
+    <t>DFAT</t>
+  </si>
+  <si>
+    <t>External_Id_Path</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>id</t>
   </si>
 </sst>
 </file>
@@ -415,42 +424,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC009C7E-7FED-434A-80FD-C4CDDA6E12F9}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/rules/sourceConfig.xlsx
+++ b/data/rules/sourceConfig.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5202C96-8C65-2C4D-9915-E37D50EAAB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5061B2B-9425-D340-9EAC-6631270D5098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15920" xr2:uid="{CD5289B5-C06B-194A-96AE-6288D441C4BC}"/>
+    <workbookView xWindow="8020" yWindow="8360" windowWidth="27640" windowHeight="15920" xr2:uid="{CD5289B5-C06B-194A-96AE-6288D441C4BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>source</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>EU-TRAVEL-BAN</t>
+  </si>
+  <si>
+    <t>subjectType.code</t>
   </si>
 </sst>
 </file>
@@ -427,6 +433,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -473,6 +480,12 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
